--- a/mistral_translate_work/split_by_prompt/excel/monster_description/lang_multi_text/lang_multi_text__monster_description__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/monster_description/lang_multi_text/lang_multi_text__monster_description__part_0001.xlsx
@@ -575,7 +575,8 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>TD được cấu tạo từ những mảnh đá vụn. Thị lực kém và có sở thích phá phách.</t>
+          <t>Một Tacet Discord được xây dựng từ những khối đá vụn. Thị lực của nó rất kém và thường xuyên điên cuồng tấn công. 
+Tiếng va chạm lạch cạch của lớp vỏ đá giúp Vanguard Junrock xác định tình hình xung quanh.</t>
         </is>
       </c>
     </row>
@@ -640,7 +641,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Một Tranquilite TD cấp Common sinh sống tại các vùng núi. Common bị bỏ qua do ngoại hình giống đá.</t>
+          <t>Một Tacet Discord cấp thường Tranquilite sinh sống ở vùng núi. Thường bị bỏ qua do hình dạng giống đá.</t>
         </is>
       </c>
     </row>
@@ -706,8 +707,8 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Một TD được cấu tạo từ những mảnh đá vụn. Thường xuất hiện cùng với Vanguard Junrock. 
-Khác với Vanguard Junrock, Fission Junrock có năng lượng hoạt động mạnh mẽ và không ổn định hơn, dễ phát nổ khi va chạm. Các ghi chép cho thấy đôi khi nó được các Tacet Discord khác sử dụng như vũ khí Dodgem.</t>
+          <t>Một TD được xây dựng từ những mảnh đá vụn. Thường xuất hiện cùng với Vanguard Junrock. 
+Khác với Vanguard Junrock, Fission Junrock mang năng lượng bất ổn và dễ phát nổ khi va chạm. Theo ghi chép, đôi khi nó còn được các Tacet Discord khác dùng làm vũ khí ném.</t>
         </is>
       </c>
     </row>
@@ -772,7 +773,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Một Tacet Discord cấp Common thuộc loại Tranquilite, sinh sống ở vùng núi. Common bị bỏ qua do hình dạng giống dung nham.</t>
+          <t>Một Tacet Discord cấp thường Tranquilite sinh sống ở vùng núi. Thường bị bỏ qua do hình dạng giống dung nham.</t>
         </is>
       </c>
     </row>
@@ -837,7 +838,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Một TD Whisperin cấp Common thường xuất hiện ở vùng hoang dã. Các ghi chép cho thấy nó có khả năng kéo dây cung như con người và bắn sét như mũi tên.</t>
+          <t>Một Tacet Discord cấp thường lang thang nơi hoang dã. Ghi chép cho thấy nó có khả năng kéo dây cung như con người và bắn tia sét như mũi tên.</t>
         </is>
       </c>
     </row>
@@ -902,7 +903,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Một WhisperinTD cấp Common thường xuất hiện trong hoang dã. Hồ sơ cho thấy nó có thể tập trung năng lượng Glacio để tạo thành "vật phóng" và Dodgem như con người.</t>
+          <t>Một Tacet Discord cấp thường lang thang nơi hoang dã. Ghi chép cho thấy nó có thể tập trung năng lượng Glacio để tạo thành "vật phóng" và ném đi như con người.</t>
         </is>
       </c>
     </row>
@@ -967,7 +968,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Một TD Thì Thầm cấp Common gặp ở vùng hoang dã. Các ghi chép cho thấy nó có thể gom gió thành những chiếc boomerang để Dodgem và tấn công như con người.</t>
+          <t>Một Tacet Discord cấp thường lang thang nơi hoang dã. Ghi chép cho thấy nó có thể gom gió thành những chiếc boomerang và ném tấn công như con người.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1033,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Whisperin cấp Common thường thấy trong tự nhiên. Hồ sơ cho thấy một lưỡi kiếm sắc bén mọc ra từ cánh tay của nó.</t>
+          <t>Một Tacet Discord cấp thường gặp ngoài hoang dã. Theo ghi chép, một lưỡi kiếm sắc bén mọc ra từ cánh tay của nó.</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1098,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>WhisperinTD cấp Common thường gặp trong tự nhiên. Theo ghi chép, một lưỡi hái khổng lồ mọc ra từ cánh tay của nó.</t>
+          <t>Một Tacet Discord cấp thường gặp ngoài hoang dã. Theo ghi chép, một lưỡi hái khổng lồ mọc ra từ cánh tay của nó.</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1163,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Một loài Tacet Discord Whisperin cấp Common phổ biến trong tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Fusion để tấn công.</t>
+          <t>Một Tacet Discord cấp thường phân bố rộng rãi ngoài tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Fusion để tấn công.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Whisperin cấp Common phân bố rộng rãi trong tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Spectro để tấn công.</t>
+          <t>Một Tacet Discord cấp thường phân bố rộng rãi ngoài tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Spectro để tấn công.</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1293,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Một TD Whisperin cấp Common phân bố rộng rãi trong tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Aero để tấn công.</t>
+          <t>Một Tacet Discord cấp thường phân bố rộng rãi ngoài tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Aero để tấn công.</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1358,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Một TD Whisperin hạng Common phân bố rộng rãi trong tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Havoc để tấn công.</t>
+          <t>Một Tacet Discord cấp thường phân bố rộng rãi ngoài tự nhiên. Nó có thể sử dụng một lượng nhỏ năng lượng Havoc để tấn công.</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1423,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common phân bố rộng rãi ở các khu vực thủy vực. Kích thước của nó tương đối nhỏ.</t>
+          <t>Một Tacet Discord cấp thường Howler phân bố rộng rãi ở các khu vực nước. Kích thước của nó tương đối nhỏ.</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1488,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Một Tacet Discord cấp Common thuộc loại Tranquilite, thường tụ tập ngoài tự nhiên. Hình dạng của nó giống quặng băng.</t>
+          <t>Một Tacet Discord cấp thường Tranquilite thường tụ tập ngoài tự nhiên. Hình dạng của nó giống quặng băng.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1553,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Một TD Tranquilite cấp Common thường tụ tập trong tự nhiên. Hình dạng của nó giống như một tảng đá nham thạch.</t>
+          <t>Một Tacet Discord cấp thường Tranquilite thường tụ tập ngoài tự nhiên. Hình dạng của nó giống đá dung nham.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1618,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Một Tacet Discord thuộc lớp Common Tranquilite thường tụ tập ngoài tự nhiên. Hình dáng giống như một tảng đá vàng.</t>
+          <t>Một Tacet Discord cấp thường Tranquilite thường tụ tập ngoài tự nhiên. Hình dạng của nó giống đá vàng.</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1683,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Một TD Tranquilite hạng Common thường tụ tập ngoài tự nhiên. Hình dáng của nó giống như một mạch quặng đen tuyền.</t>
+          <t>Một Tacet Discord cấp thường Tranquilite thường tụ tập ngoài tự nhiên. Hình dạng của nó giống một mạch quặng đen tuyền.</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1748,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Một TD Howler cấp Common thường thấy lơ lửng trong tự nhiên. Sức mạnh của nó rất yếu ớt.</t>
+          <t>Một Tacet Discord cấp thường thường thấy lơ lửng ngoài hoang dã. Sức mạnh của chúng rất yếu ớt.</t>
         </is>
       </c>
     </row>
@@ -1814,9 +1815,9 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Loài động vật giống lợn rừng thường thấy trong các khu rừng, có tính cách nhạy cảm và dễ cáu kỉnh. 
-Cặp nanh sắc nhọn là giải pháp cho mọi vấn đề mà Sabyr Boar gặp phải – nó sẽ luôn lao thẳng về phía bất cứ thứ gì xâm phạm lãnh thổ của mình mà không hề do dự. 
-Một câu thành ngữ ở Huanglong cũng ví von "cú lao của Sabyr Boar" với những kẻ liều lĩnh.</t>
+          <t>Loài động vật giống lợn rừng thường thấy trong các khu rừng, bản tính nhạy cảm và dễ nổi cáu. 
+Đối với Lợn Rừng Sabyr, nanh sắc chính là giải pháp cho mọi vấn đề – bất cứ kẻ nào xâm phạm lãnh địa của nó đều sẽ bị húc tới tấp không thương tiếc. 
+Một câu thành ngữ ở Huanglong còn ví von "húc như Lợn Rừng Sabyr" để chỉ những kẻ liều lĩnh, bất chấp.</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1882,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common thường xuất hiện ở vùng hoang dã. Nó lao tới với tốc độ đáng kinh ngạc.</t>
+          <t>Một Tacet Discord cấp thường xuất hiện ngoài hoang dã. Chúng lao tới với tốc độ kinh hoàng.</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1947,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common, sống trên cạn. Kích thước của nó quyết định sức mạnh hạn chế.</t>
+          <t>Một Tacet Discord cấp thường, sống trên cạn, thuộc loại Howler. Kích thước nhỏ bé khiến sức mạnh của nó bị hạn chế.</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2012,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common thường được phát hiện ở các vùng núi. Nó thường đi theo và phối hợp với các Tacet Discord có kích thước lớn hơn.</t>
+          <t>Một Tacet Discord cấp thường xuất hiện ở vùng núi. Chúng thường đi theo và phối hợp với những Tacet Discord lớn hơn.</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2077,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Một TD Tranquilite cấp Common phân bố ở khu vực ẩm ướt. Common được phát hiện bên cạnh các cá thể trưởng thành hơn.</t>
+          <t>Một Tacet Discord cấp thường Tranquilite phân bố ở những khu vực ẩm ướt. Thường được phát hiện bên cạnh những cá thể trưởng thành hơn.</t>
         </is>
       </c>
     </row>
@@ -2142,8 +2143,8 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2209,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -2274,8 +2275,8 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2341,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -2406,8 +2407,8 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -2538,8 +2539,8 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2605,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -2670,8 +2671,8 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2737,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -2802,8 +2803,8 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2869,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -2934,8 +2935,8 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3001,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -3066,8 +3067,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3133,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -3198,8 +3199,8 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3265,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -3330,8 +3331,8 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3397,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -3462,8 +3463,8 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3529,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -3594,8 +3595,8 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Những Non-Resonators thuộc các nhóm Exile. Họ thực hiện hàng loạt nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
-Dù thường cúi đầu trước những đối thủ mạnh hơn, họ lại rất thành thạo trong việc đối phó với các nhóm Exile khác.</t>
+          <t>Những nhóm Resonator bị lưu đày thường thực hiện các nhiệm vụ thông thường như chiến đấu, tuần tra và thu thập vật phẩm cho đội.
+Dù thường phải cúi đầu trước những đối thủ mạnh hơn, họ lại là những chuyên gia trong việc đối phó với các nhóm lưu đày khác.</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3661,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Những Exile thường gặp lang thang trên vùng hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
+          <t>Những kẻ Lưu Đày Thường lang thang nơi hoang dã của các quốc gia. Chủ yếu hoạt động theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3726,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common sống du mục khắp Dim Forest. Các cá thể sống theo bầy đàn và đi theo một thủ lĩnh. Có khả năng bắt chước cách con người sử dụng các công cụ đơn giản.</t>
+          <t>Một Tacet Discord cấp thường lang thang khắp Rừng Mù. Chúng sống theo bầy đàn và tuân theo thủ lĩnh. Có khả năng bắt chước cách con người sử dụng các công cụ đơn giản.</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3791,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common sống trong môi trường tối tăm. Hồ sơ cho thấy nó sở hữu khả năng phản công ấn tượng.</t>
+          <t>Một Tacet Discord cấp thường sống trong môi trường tối tăm. Theo ghi chép, chúng sở hữu khả năng phản công ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3856,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Một Tacet Discord cấp Common thuộc loại Howler, thường được phát hiện ở vùng nước nông. Dựa trên các ghi chép về việc chủ động tấn công con người, nó có thể có tính khí khá nóng nảy.</t>
+          <t>Một Tacet Discord cấp thường được phát hiện ở vùng nước nông. Theo ghi chép về việc chúng chủ động tấn công con người, có lẽ chúng có tính khí khá nóng nảy.</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3921,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Một loài Tacet Discord Howler cấp Common phân bố rộng rãi trong tự nhiên. Các cá thể thường hoạt động theo nhóm và tấn công theo sự chỉ huy của con đầu đàn.</t>
+          <t>Một Tacet Discord cấp thường Howler phân bố rộng rãi trong tự nhiên. Chúng thường hoạt động theo bầy và lao vào tấn công theo con đầu đàn.</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3986,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Những tín đồ trung thành của Fractsidus, thường hợp tác với các Artificer đồng đạo. Họ sử dụng những chiếc búa khổng lồ để đẩy lùi kẻ thù.</t>
+          <t>Những tín đồ trung thành của Fractsidus, thường hợp tác với các Artificer đồng môn. Họ sử dụng những chiếc búa khổng lồ để đẩy lùi kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4051,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common sống du mục khắp Rừng Mờ. Các cá thể sống theo bầy và đi theo một thủ lĩnh. Chúng thể hiện tính lãnh thổ rất mạnh mẽ.</t>
+          <t>Một Tacet Discord cấp thường lang thang khắp Rừng Mù. Chúng sống theo bầy đàn và tuân theo thủ lĩnh. Có tính lãnh thổ rất cao.</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4116,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Những tín đồ trung thành của Fractsidus, thường hợp tác với các Artificer đồng nghiệp. Họ có thể dễ dàng sử dụng những khẩu đại bác khổng lồ.</t>
+          <t>Những tín đồ trung thành của Fractsidus, thường hợp tác với các Artificer đồng môn. Họ có thể dễ dàng sử dụng những khẩu đại bác khổng lồ.</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4181,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Những tín đồ tận tụy của Fractsidus, thường hợp tác với các Artificer đồng đạo. Chúng chiến đấu bằng súng gắn liền với tứ chi.</t>
+          <t>Những tín đồ trung thành của Fractsidus, thường hợp tác với các Artificer đồng môn. Họ chiến đấu bằng súng gắn liền trên tay chân.</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4246,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Một loài Tacet Discord Howler cấp Common bản địa của Port City of Guixu. Các ghi chép cho thấy nó có hình dáng giống với các vật thể từ nền văn minh đã mất của thành phố.</t>
+          <t>Một Tacet Discord cấp thường có nguồn gốc từ Thành Phố Cảng Guixu. Theo ghi chép, chúng có hình dáng giống với các vật thể từ nền văn minh đã mất của thành phố.</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4311,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Một TD Howler cấp Common. Nó sinh sống ở các khu vực bên dưới lãnh nguyên và rất giỏi trong việc đào các đường hầm ngầm rộng lớn.</t>
+          <t>Một Tacet Discord cấp thường Howler. Nó sinh sống dưới vùng lãnh nguyên và rất giỏi đào những đường hầm ngầm rộng lớn.</t>
         </is>
       </c>
     </row>
@@ -4377,9 +4378,9 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Một Tacet Discord bắt chước loài đà điểu đặc hữu sống tại Mt. Firmament. Không biết bay và không có sức chịu đựng cao, nó chỉ có thể sống sót ở những khu vực dưới sống núi.
-Tên của nó có hai nguồn gốc từ ngữ trong hệ ngôn ngữ Huanglong. Một bắt nguồn từ mô tả trong Hồng Chân Ký Lục: "Loài Tacet Discord bắt chước đà điểu này mập mạp và có vẻ thiếu trí thông minh."
-Nguồn gốc khác bắt nguồn từ phương ngữ địa phương. Người dân địa phương dùng từ này để mô tả những sinh vật "trông ngốc nghếch."</t>
+          <t>Một Tacet Discord bắt chước loài đà điểu đặc hữu sống tại Núi Firmament. Không biết bay và sức chịu đựng kém, nó chỉ có thể tồn tại ở những khu vực dưới sườn núi.
+Tên gọi của nó có hai nguồn gốc từ ngữ trong hệ ngôn ngữ Huanglong. Một bắt nguồn từ mô tả trong Hồng Chân Biên Niên Sử: "Loài Tacet Discord bắt chước đà điểu này mập mạp và có vẻ thiếu trí tuệ."
+Nguồn gốc khác xuất phát từ phương ngữ địa phương. Người dân dùng từ này để chỉ những sinh vật "trông ngốc nghếch".</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4445,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Common. Dù có cánh, nó hoàn toàn sống trên cạn và rất nhạy cảm với cái lạnh.</t>
+          <t>Một Tacet Discord cấp thường Howler. Dù có cánh, nó hoàn toàn sống trên cạn và rất nhạy cảm với cái lạnh.</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4510,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Một TD bắt chước đá với Fool's Gold trên lưng. Nó thường bị nhầm lẫn với quặng vàng chưa khai thác.</t>
+          <t>Một Tacet Discord bắt chước đá với Fool's Gold trên lưng. Nó thường bị nhầm là quặng vàng chưa khai thác.</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4575,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Một Tacet Discord bắt chước loài rpck, mang theo Resonant Calcite. Năng lượng Tàn Dư bên trong phát sáng với ánh lấp lánh như ngọc trai.</t>
+          <t>Một Tổ Tacet bắt chước đá cuội, chứa Calcite Cộng Hưởng bên trong. Dòng Năng Lượng Tàn Dư tỏa sáng lấp lánh như ngọc trai.</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4640,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Một TD khoáng vật thường thấy trong các mạch mỏ, chứa đựng những luồng khí mạnh mẽ.</t>
+          <t>Một Tổ Tacet khoáng chất thường thấy trong các mạch mỏ, chứa đựng những luồng khí mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -4705,8 +4706,8 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Một Echoes cầm kiếm giống như bức tượng câm lặng và nghiêm nghị, có nhiệm vụ bảo vệ hòa bình và an toàn cho Ragunna City theo mệnh lệnh của Order.
-Dưới sự giám sát của nó, bất kỳ cá nhân hoặc Echoes khả nghi nào cũng sẽ bị bắt giữ ngay lập tức và đưa đến Chamber of Discipline để đảm bảo an ninh cho thành phố.</t>
+          <t>Một Cộng Hưởng Giả cầm kiếm, trông như bức tượng nghiêm nghị và im lặng, có nhiệm vụ bảo vệ hòa bình và an toàn cho Ragunna City theo mệnh lệnh của Order.
+Dưới sự giám sát của nó, bất kỳ cá nhân hay Cộng Hưởng Giả khả nghi nào cũng sẽ bị bắt giữ ngay lập tức và đưa đến Phòng Kỷ Luật để đảm bảo an ninh cho thành phố.</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4772,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Một Echo cầm kiếm giống như bức tượng im lặng và nghiêm nghị, có nhiệm vụ bảo vệ hòa bình và an toàn cho Ragunna City theo mệnh lệnh của Order.</t>
+          <t>Một Cộng Hưởng Giả cầm kiếm, trông như bức tượng nghiêm nghị và im lặng, có nhiệm vụ bảo vệ hòa bình và an toàn cho Ragunna City theo mệnh lệnh của Order.</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4837,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Một Echo cầm cung giống như bức tượng, có nhiệm vụ giám sát Thành phố Ragunna và báo cáo chi tiết về Order.</t>
+          <t>Một Echo cầm cung giống như bức tượng, có nhiệm vụ giám sát Thành phố Ragunna và báo cáo chi tiết về Hội.</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4902,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Một Echo giống như bức tượng tượng trưng cho lòng thương xót và từ bi, luôn lắng nghe những lời cầu nguyện và ca ngợi của người Ragunnesi dâng lên Order.</t>
+          <t>Một Echo giống như bức tượng, tượng trưng cho lòng nhân từ và từ bi, luôn lắng nghe những lời cầu nguyện và ca tụng của người Ragunnesi dâng lên Giáo Hội.</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4967,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Một TD bắt chước hình dáng rồng con, với những luồng gió xoáy giữa các móng vuốt. Thường sống theo đàn ở vùng hoang dã.</t>
+          <t>Một Tacet Discord bắt chước hình dáng con non của drake, với những luồng gió xoáy giữa những móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5032,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Một Tacet Discord bắt chước hình dạng con non của loài rồng, với những tia sét lóe lên giữa các móng vuốt. Thường sống theo đàn trong hoang dã.</t>
+          <t>Một Tacet Discord bắt chước hình dáng con non của drake, với những tia sét lóe lên giữa những móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5097,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Một TD bắt chước hình dáng con non của loài drake, với băng và sương giá hình thành giữa các móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
+          <t>Một Tacet Discord bắt chước hình dáng con non của drake, với băng giá và sương giá kết tụ giữa những móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5162,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Một TD bắt chước hình dáng con non của loài drake, với ngọn lửa bùng cháy giữa các móng vuốt, thường sống theo đàn trong hoang dã.</t>
+          <t>Một Tacet Discord bắt chước hình dáng con non của drake, với ngọn lửa rực cháy giữa những móng vuốt, thường sống theo bầy đàn trong hoang dã.</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5227,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Một Tacet Discord bắt chước hình dạng con thú rồng non, với ánh sáng nhấp nháy giữa các móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
+          <t>Một Tacet Discord bắt chước hình dáng con non của drake, với ánh sáng nhấp nháy giữa những móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5292,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Một TD bắt chước hình dáng một con drake con, với những dòng xoáy đen tối trải dài giữa các móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
+          <t>Một Tacet Discord bắt chước hình dáng con non của drake, với những dòng chảy u ám trải dài giữa những móng vuốt. Thường sống theo bầy đàn trong hoang dã.</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5357,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Với san hô làm xương, rong biển làm thịt, và niềm tin mù quáng làm chất xúc tác, chúng là hiện thân ký hiệu của tín ngưỡng Thủy Triều Đen, những cái xác được khâu vá từ đống đổ nát.</t>
+          <t>Với san hô làm xương, rong biển làm thịt, và niềm tin mù quáng làm chất xúc tác, chúng là hiện thân ký ức của tín ngưỡng Thủy Triều Đen, những xác sống được khâu vá từ đống đổ nát.</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5422,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Những Fractsidus gunners có thân thể trở nên lạnh lẽo khi số phận vang lên một hợp âm bất hòa. Sau khi mất kiểm soát dưới đáy biển sâu, chúng không bao giờ có thể trở lại như xưa.</t>
+          <t>Những xạ thủ Fractsidus có da thịt lạnh ngắt khi vận mệnh chạm phải nốt trầm sai. Sau khi mất kiểm soát dưới đáy biển sâu, họ không bao giờ trở lại được như xưa.</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Tranquilite cấp Elite được tìm thấy ở các vùng núi. Chúng có kích thước khổng lồ và sinh sống trong các tảng đá.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Tranquilite xuất hiện ở vùng núi non. Chúng có kích thước khổng lồ và thường trú ngụ trong các tảng đá.</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5552,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Elite xuất hiện ở các khu rừng và bờ biển. Bản tính hung hăng của chúng thường thể hiện qua những hành động dữ dội.</t>
+          <t>Một Tacet Discord Sói Cấp Cao xuất hiện ở rừng và bờ biển. Bản tính hung hăng của chúng thường thể hiện qua những hành động dữ dội như sấm truyền.</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5617,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Elite được tìm thấy trong các khu rừng và bờ biển. Bản tính hung hăng của chúng thường thể hiện qua những động tác dữ dội như bão tố.</t>
+          <t>Một Tacet Discord Sói Cấp Cao xuất hiện ở rừng và bờ biển. Bản tính hung hăng của chúng thường bộc lộ qua những đòn tấn công như bão tố.</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5682,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Một TD Whisperin cấp Elite thường thấy trong tự nhiên. Hồ sơ ghi chép cho thấy nó trông giống một nhạc công cầm sáo.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Whisperin thường thấy trong tự nhiên. Theo ghi chép, nó trông giống một nhạc công đang cầm sáo.</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5747,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Một Whisperin TD cấp Elite thường xuất hiện trong tự nhiên. Hồ sơ ghi lại rằng nó trông giống một nhạc công cầm trống lục lạc trên tay.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Whisperin thường thấy trong tự nhiên. Theo ghi chép, nó trông giống một nhạc công đang cầm trống lục lạc.</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5812,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Một Whisperin TD cấp Elite với ngoại hình giống con người. Với kích thước khổng lồ như một tảng đá nguyên khối, nó thường được phát hiện trong tự nhiên.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Whisperin có hình dáng giống người. Với kích thước khổng lồ như một tảng đá nguyên khối, nó thường xuất hiện trong tự nhiên.</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5877,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Một Tacet Discord thuộc lớp Elite Whisperin với hình dạng giống con người. Với kích thước khổng lồ như một pháo đài, thường được phát hiện trong hoang dã.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Whisperin có hình dáng giống người. Với kích thước đồ sộ như một pháo đài, nó thường xuất hiện trong tự nhiên.</t>
         </is>
       </c>
     </row>
@@ -5942,8 +5943,8 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Loài sinh vật giống lưỡng cư cỡ lớn chủ yếu được tìm thấy trong các khu rừng. Da cứng của chúng tỏa ra sức nóng bỏng rát.
-Nghiên cứu cho thấy độ dẻo dai của da Viridblaze Saurian có mối tương quan thuận với nhiệt độ cơ thể của chúng.</t>
+          <t>Loài sinh vật giống ếch nhái, thường xuất hiện trong rừng. Da chúng cứng cáp và tỏa ra sức nóng như thiêu đốt. 
+Nghiên cứu cho thấy độ dẻo dai của da Viridblaze Saurian tỉ lệ thuận với nhiệt độ cơ thể của chúng.</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6009,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Tranquilite cấp Elite phân bố tại các vùng đầm lầy. Không có hồ sơ nào ghi nhận việc TD này tự di chuyển.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Tranquilite phân bố tại các vùng đầm lầy. Không có ghi chép nào về việc TD này tự di chuyển.</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6074,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Một TD Howler cấp Common phân bố rộng rãi trong tự nhiên. Các cá thể thường hoạt động theo nhóm và loại TD này thường dẫn đầu các đợt tấn công.</t>
+          <t>Một Tacet Discord cấp thường Howler phân bố rộng rãi trong tự nhiên. Chúng thường hoạt động theo bầy và cá thể này thường dẫn đầu các đợt tấn công.</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6139,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Một TD Howler Cấp Cao sống du mục khắp Dim Forest. Các cá thể sống theo bầy đàn. Hồ sơ ghi lại rằng TD này có thể uốn nắn sức mạnh của gió theo ý muốn và tấn công bằng nó.</t>
+          <t>Một Tacet Discord Sói Cấp Cao sống du mục khắp Rừng Mù. Chúng sống theo bầy đàn. Theo ghi chép, loài Tacet Discord này có thể điều khiển sức gió và tấn công bằng nó.</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6204,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Động vật hung dữ giống gấu đen. Đầu và vai của chúng phủ đầy các cụm Tacetite sắc nhọn hình mũi tên, như những chiếc gai bất khả xâm phạm.</t>
+          <t>Loài thú dữ trông như gấu đen hung tợn. Đầu và vai chúng phủ đầy những mảng Tacetite sắc nhọn hình mũi tên, như những gai chông bất hoại.</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6269,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Một loài Tacet Discord Howler cấp Elite sinh sống trong rừng. Nó thường ở trạng thái cảnh giác cao độ.</t>
+          <t>Một Tacet Discord Sói Cấp Cao cư ngụ trong rừng. Nó thường cảnh giác cao độ.</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6334,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Howler cấp Elite ẩn mình trong đống đổ nát thành phố. Hồ sơ ghi nhận rằng phương pháp ngụy trang đặc biệt của nó gây ra nhiều khó khăn cho những người muốn xác định nó.</t>
+          <t>Một Tacet Discord Sói Cấp Cao ẩn nấp trong đống đổ nát thành phố. Theo ghi chép, khả năng ngụy trang đặc biệt của nó gây không ít khó khăn cho những ai muốn nhận diện.</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6399,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Những thủ lĩnh của Exiles, thường được tìm thấy tại các khu cắm trại Exile. Họ có nhiều kinh nghiệm chiến đấu và kỹ năng hơn so với các Exiles thông thường.</t>
+          <t>Những thủ lĩnh của nhóm Lưu Đày, thường xuất hiện tại Khu Trại Lưu Đày. Họ có nhiều kinh nghiệm và kỹ năng chiến đấu hơn so với các Lưu Đày thông thường.</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6464,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Thành viên kỹ thuật của nhóm Exiles, thường được tìm thấy tại các khu cắm trại của Exiles. Họ phụ trách sửa chữa và chế tạo vũ khí cùng trang bị.</t>
+          <t>Các thành viên Kỹ thuật viên của nhóm Lưu Đày, thường xuất hiện tại các trại Lưu Đày. Họ phụ trách sửa chữa và chế tạo vũ khí, trang bị.</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6594,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Một TD Howler cấp Elite sống du mục khắp Dim Forest. Các cá thể sống theo bầy đàn. Các ghi chép cho thấy TD này rất hung hăng và có xu hướng trộm cắp đồ vật của con người.</t>
+          <t>Một Tacet Discord Sói Cấp Cao sống du mục khắp Rừng Mù. Chúng sống theo bầy đàn. Theo ghi chép, loài Tacet Discord này tính khí bất ổn và thường xuyên trộm cắp đồ vật của con người.</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6659,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Một TD Howler cấp Elite ẩn náu tại Thành phố Cảng Guixu. Nó cải trang thành một phương tiện bọc thép bị bỏ hoang.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Howler, ẩn mình tại Thành phố Cảng Guixu. Nó cải trang thành một chiếc xe bọc thép bị bỏ hoang.</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6724,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Một TD Howler hạng Elite phân bố rộng rãi trên vùng tuyết địa. Glacio Dreadmanes là TD sống theo bầy đàn và thường di chuyển theo đàn.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Howler phân bố rộng rãi trên vùng băng tuyết. Glacio Dreadmane là loại TD sống theo bầy đàn và thường di chuyển theo nhóm.</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6789,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Một cấu trúc cơ khí canh giữ các tàn tích trên Mt. Firmament. Nó nhận lệnh trực tiếp từ Sentinel và hoạt động như người bảo vệ của họ.</t>
+          <t>Một cấu trúc cơ khí canh giữ tàn tích trên Núi Firmament. Nó nhận lệnh trực tiếp từ Sentinel và hoạt động như người bảo vệ của họ.</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6854,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Howler cấp Elite. Nó sống đơn độc và để lại những dấu vết phát sáng khi di chuyển.</t>
+          <t>Một Tacet Discord hạng Elite thuộc loại Howler. Nó sống đơn độc và để lại những vệt sáng khi di chuyển.</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6919,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Một Discord hình người với cơ thể được lắp ráp từ những mảnh kính màu vỡ. Ánh sáng lấp lánh tỏa ra từ cơ thể mỗi khi nó di chuyển.</t>
+          <t>Một Tacet Discord hình người với thân thể ghép từ những mảnh kính màu vỡ vụn. Mỗi cử động đều tỏa ra những tia sáng lấp lánh.</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6984,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Một Tacet Discord tượng đá thể hiện sự giải cấu trúc và tái cấu trúc. Động tác của nó chậm chạp và vụng về.</t>
+          <t>Một Tổ Tacet bằng đá, tượng trưng cho sự giải cấu trúc và tái cấu trúc. Động tác của nó chậm chạp và vụng về.</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7049,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Một TD bắt chước gấu hung dữ với sức mạnh phi thường, vung tay với lực như bão táp.</t>
+          <t>Một Tacet Discord bắt chước gấu với sức mạnh khủng khiếp, vung vẩy như bão táp.</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7114,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Nó nắm quyền chỉ huy các Echoes khác thuộc Order, thực thi ý chí của Order để tiêu diệt mọi kẻ vi phạm.</t>
+          <t>Nó nắm quyền điều khiển các Echo khác của Order, thực thi ý chí của Order để loại bỏ mọi kẻ phản bội.</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7179,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Những Tacet Discord lưỡng cư hung dữ bắt chước Saurosuchus. Được đặt tên theo hàng sừng bao phủ cơ thể chúng.</t>
+          <t>Tacet Discord hung tợn, lưỡng cư, bắt chước loài Saurosuchus. Được đặt tên theo những hàng sừng phủ kín cơ thể chúng.</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7244,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Với san hô làm xương, rong biển làm thịt và niềm tin mù quáng làm chất xúc tác, chúng là hiện thân ký hiệu của tín ngưỡng Dark Tide, những pháp sư truyền đạt ý chí của Dark Tide.</t>
+          <t>Với san hô làm xương, rong biển làm thịt, và niềm tin mù quáng làm chất xúc tác, chúng là hiện thân ký ức của tín ngưỡng Thủy Triều Đen, những pháp sư ngân vang ý chí của Thủy Triều Đen.</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7309,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Những đấu sĩ của Septimont chiến đấu không giới hạn, thể hiện niềm đam mê bất diệt của người chiến binh.</t>
+          <t>Những chiến binh Septimont tự do chiến đấu, mang trong mình ngọn lửa bất diệt của người lính.</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7374,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Những đấu sĩ của Septimont chiến đấu không giới hạn, thể hiện ý chí tự do.</t>
+          <t>Những chiến binh Septimont tự do chiến đấu, thể hiện ý chí tự do bất khuất.</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7439,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Những đấu sĩ của Septimont chiến đấu không giới hạn, theo đuổi lý tưởng công lý.</t>
+          <t>Những chiến binh Septimont tự do chiến đấu, bảo vệ lý tưởng công lý.</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7504,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Những đấu sĩ của Septimont chiến đấu không giới hạn, mang trong mình quyết tâm không khuất phục.</t>
+          <t>Những đấu sĩ Septimont chiến đấu không ngừng nghỉ, mang trong mình ý chí bất khuất.</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7569,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Những đấu sĩ của Septimont chiến đấu không giới hạn, tin theo chủ nghĩa vô ngã.</t>
+          <t>Những chiến binh Septimont tự do chiến đấu, tin vào giáo lý vô ngã.</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7634,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Những Thanh Tra của Fractsidus, khoác lên mình những tua tối phát ra từ cơ thể cải tiến cao cấp như một huy hiệu danh dự.</t>
+          <t>Những Thanh Tra Viên của Fractsidus, khoác lên mình những tua tối đến từ cơ thể cải tiến như một huy hiệu danh dự.</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7699,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Một Whisperin TD cấp Overlord ẩn náu tại Central Plains. Nó thể hiện khả năng chiến đấu tương tự như con người.</t>
+          <t>Một Tacet Discord cấp Overlord loại Whisperin ẩn nấp ở Central Plains. Nó thể hiện khả năng chiến đấu tương tự như con người.</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7764,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Một TD Thì Thầm cấp Thống Soái nằm tại Thành phố Cảng Guixu. Những ghi chép duy nhất hiện có ghi nhận phương thức di chuyển độc đáo của nó so với các Tacet Discord khác.</t>
+          <t>Một Tacet Discord cấp Overlord loại Whisperin xuất hiện ở Thành Phố Cảng Guixu. Những ghi chép duy nhất còn lại cho thấy nó có phương thức di chuyển độc nhất vô nhị trong số các Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7829,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Overlord xuất hiện tại Desorock Highland. Được biết đến là hung dữ và có tính tấn công cao.</t>
+          <t>Một Tacet Discord cấp Overlord loại Howler xuất hiện ở Desorock Highland. Nó nổi tiếng hung dữ và cực kỳ hung hãn.</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7894,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Một Tacet Discord cấp Overlord thuộc loại Howler, nằm im lìm dưới Tiger's Maw. Nó dụ con mồi vào sâu trong màn sương nơi nó ẩn nấp trước khi bắt giữ.</t>
+          <t>Một Tacet Discord cấp Overlord loại Howler đang nằm im dưới Họng Hổ. Nó dụ con mồi vào sâu trong màn sương nơi nó ẩn nấp trước khi bắt gọn.</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7959,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Một Tacet Discord Howler cấp Overlord tại Dim Forest. Với kích thước to lớn, nó là bá chủ của vùng đất này.</t>
+          <t>Một Tacet Discord cấp Overlord loại Howler trong Rừng Âm U. Với kích thước khổng lồ, nó tự xưng bá chủ vùng đất này.</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8024,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Một TD Whisperin cấp Overlord được tìm thấy bên ngoài Gorges of Spirit. Được biết đến là hung hăng, ác ý và hiếu chiến. Cần quan sát thêm để hiểu rõ hơn về sinh vật này.</t>
+          <t>Một Tacet Discord cấp Overlord loại Whisperin được tìm thấy bên ngoài Hẻm Núi Linh Hồn. Được biết là hung hăng, độc ác và rất hiếu chiến. Cần quan sát thêm để hiểu rõ hơn về sinh vật này.</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8089,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Một TD Hú Họa cấp Thảm Họa nằm im lìm tại Gorges of Spirit. Do nó hoàn toàn không hoạt động, các ghi chép về hành vi của nó rất khan hiếm.</t>
+          <t>Một Tacet Discord cấp Thảm Họa loại Howler nằm im lìm trong Gorges of Spirit. Do nó hoàn toàn bất động, các ghi chép về hành vi của nó rất hiếm hoi.</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8154,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Một Howler TD cấp Calamity ẩn sâu dưới lòng biển. Những giai điệu do nó tạo ra được ghi lại và phát hiện có Dodget tương đồng với tiếng hát của cá voi.</t>
+          <t>Một Tacet Discord cấp Thảm Họa loại Howler ẩn sâu dưới lòng biển. Những giai điệu nó tạo ra được ghi lại và phát hiện giống như tiếng cá voi hát.</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8219,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Dạng đặc biệt của một trong những Overseer của Fractsidus. Quái vật này sử dụng lưỡi hái đen ngòm để chém xuyên qua trật tự và luật lệ.</t>
+          <t>Một dạng đặc biệt của Fractsidus Overseer. Quái vật này sở hữu lưỡi hái đen ngòm, có thể xé nát trật tự và luật lệ.</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8284,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Một Staticoid TD ẩn náu bên dưới một cơ sở CSC bị bỏ hoang, hình dạng vật lý của nó là tập hợp của nhiều vật thể khác nhau. Mức độ đe dọa: Overlord Class.</t>
+          <t>Một Tacet Discord dạng Staticoid ẩn nấp dưới cơ sở CSC bỏ hoang, thân thể của nó là tập hợp của vô số vật thể khác nhau. Mức độ đe dọa: Hạng Overlord.</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8349,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Một TD Whisperin được phát hiện tại Norfall Barrens, thể hiện những đặc điểm nổi bật hơn của hình dạng phụ nữ. Có nghi ngờ liên quan đến Threnodian, được bao quanh bởi các tập hợp phụ loài TD khác. Do môi trường nguy hiểm, thông tin và ghi chép vẫn còn thiếu, nó đã được xếp vào loại Calamity Class.</t>
+          <t>Một Tacet Discord dạng Whisperin được phát hiện ở Norfall Barrens, mang đặc điểm nổi bật của hình dáng phụ nữ. Có nghi vấn liên quan đến Threnodian, bao quanh bởi các tập hợp phụ TD khác. Do môi trường nguy hiểm, thông tin và ghi chép vẫn còn thiếu sót, nó đã được xếp vào hạng Calamity Class.</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8414,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Một Tacet Discord thuộc lớp Overlord Whisperin được tìm thấy tại Desorock Highland. Nó thể hiện khả năng chiến đấu tương tự như con người.</t>
+          <t>Một Tacet Discord cấp Overlord loại Whisperin được phát hiện ở Desorock Highland. Nó thể hiện khả năng chiến đấu tương tự như con người.</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8479,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Một trong những Sentinel tại Huanglong mang hình dáng của Loong. Với khả năng thao túng thời gian, Jué dẫn dắt sự phát triển của nền văn minh Jinzhou.</t>
+          <t>Một trong các Sentinel ở Huanglong, mang hình dáng của Loong. Với khả năng thao túng thời gian, Jué dẫn dắt sự phát triển của nền văn minh Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8544,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hàng phòng thủ cuối cùng được xây dựng bởi Hệ thống Tethys, tuần tra biên giới giữa thực tại và thế giới kỹ thuật số.</t>
+          <t>Tuyến phòng thủ cuối cùng do Hệ thống Tethys dựng nên, tuần tra biên giới giữa thực tại và thế giới số.</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8609,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Một Discord giống sói thống trị các vùng cao nguyên, nổi tiếng với bản năng săn mồi không ngừng nghỉ.</t>
+          <t>Một Tacet Discord giống sói thống trị vùng cao, nổi tiếng với bản tính săn mồi không ngừng nghỉ.</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8674,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Một Discord giống sói lang thang ở những vùng bị bão táp, nổi tiếng với tính hung hăng và tốc độ như chớp.</t>
+          <t>Một Tacet Discord giống sói lang thang vùng bão tố, nổi tiếng với tính hung hăng và tốc độ như chớp.</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8739,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Một Discord giống sói hoành hành ở các vùng băng giá, nổi tiếng với bản tính lạnh lùng và tàn nhẫn.</t>
+          <t>Một Tacet Discord giống sói hoành hành vùng băng giá, nổi tiếng với bản tính lạnh lùng và tàn nhẫn.</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8804,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Một Discord đóng vai trò "đầu" của Chop Chop.</t>
+          <t>Một Tacet Discord đóng vai trò như "đầu" của Chop Chop.</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8869,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Một Discord đóng vai trò "bàn tay trái" của Chop Chop.</t>
+          <t>Một Tacet Discord đóng vai trò "cánh tay trái" của Chop Chop.</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8934,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Một Discord đóng vai trò "cánh tay phải" của Chop Chop.</t>
+          <t>Một Tacet Discord đóng vai trò "cánh tay phải" của Chop Chop.</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8999,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Một Discord hình chim săn mồi tại Penitent's End. Trong bóng tối, hình dạng của nó hòa vào bóng đêm, chỉ còn chiếc mặt nạ lấp lánh như ignis fatuus.</t>
+          <t>Một Tacet Discord hình chim săn mồi ở Penitent's End. Trong bóng tối, thân hình nó hòa vào màn đêm, chỉ còn chiếc mặt nạ lập lòe như đom đóm ma trơi.</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9064,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Từng là sinh vật còn sót lại trong Nimbus Sanctum, nó phân rã thành Discord khi tần số của nó suy yếu, khiến nó lang thang trong nỗi buồn vĩnh cửu.</t>
+          <t>Từng là một sinh vật còn sót lại trong Nimbus Sanctum, nó đã thoái hóa thành Tacet Discord khi tần số của nó dần tàn lụi, để lại một linh hồn lang thang trong nỗi sầu muộn bất tận.</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9129,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Một Discord vô hình trú ngụ trong cơ thể của một con thú nhồi bông quyến rũ và điển trai.</t>
+          <t>Một Tacet Discord vô hình trú ngụ trong thân xác của một con thú nhồi bông duyên dáng và phong độ.</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9194,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Một Discord vô hình trú ngụ trong cơ thể của một con thú nhồi bông hiền lành, giàu lòng trắc ẩn.</t>
+          <t>Một Tacet Discord vô hình trú ngụ trong thân xác của một món đồ chơi nhồi bông hiền lành, trầm lặng.</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9259,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Một Discord vô hình trú ngụ trong cơ thể của một con thú nhồi bông chăm chỉ, bền bỉ. Nó sống nhờ vào niềm tin và lòng biết ơn mà đôi tay lao động của nó kiếm được—những tần số mà nó thấy ngon lành nhất.</t>
+          <t>Một Tacet Discord vô hình trú ngụ trong thân xác của một món đồ chơi nhồi bông chắc chắn, cần mẫn. Hắn sống bằng niềm tin và lòng biết ơn mà đôi tay chăm chỉ của hắn kiếm được—những tần số mà hắn thấy ngon lành nhất.</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9324,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Một Discord vô hình trú ngụ trong cơ thể của một con thú nhồi bông chắc chắn và chăm chỉ.</t>
+          <t>Một Tacet Discord vô hình trú ngụ trong thân xác của một món đồ chơi nhồi bông chắc chắn, cần mẫn.</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9389,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Một Discord ngụy trang thành rương tiếp tế, lợi dụng lòng tham của nạn nhân và nuốt chửng những kẻ đến gần.</t>
+          <t>Một Tacet Discord ngụy trang thành rương tiếp tế, rình mồi bằng lòng tham của nạn nhân rồi nuốt chửng kẻ nào đến gần.</t>
         </is>
       </c>
     </row>
@@ -9453,7 +9454,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Một Discord hình người mặc trang phục sang trọng, sử dụng lưỡi kiếm sắc bén và sức mạnh phi thường chỉ tồn tại trong truyền thuyết.</t>
+          <t>Một Tacet Discord hình người khoác bộ trang phục sang trọng, vung lưỡi kiếm sắc bén và sức mạnh phi thường chỉ tồn tại trong truyền thuyết.</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9519,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>TD dạng người mặc trang phục tinh xảo, sử dụng một lưỡi kiếm sắc bén. Chỉ được nhìn thấy dưới ánh sáng mặt trời.</t>
+          <t>Một Tacet Discord hình người khoác bộ trang phục sang trọng, vung lưỡi kiếm sắc bén. Chỉ hiện diện dưới ánh sáng rực rỡ của mặt trời.</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9584,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Một Discord hình người mặc trang phục sang trọng, cầm lưỡi kiếm sắc bén. Chỉ được nhìn thấy dưới ánh sáng nhợt nhạt của mặt trăng.</t>
+          <t>Một Tacet Discord hình người khoác bộ trang phục sang trọng, vung lưỡi kiếm sắc bén. Chỉ xuất hiện dưới ánh trăng mờ ảo.</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9649,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Một Discord hình người sinh ra từ biển sâu, mang hình dáng của một quý tộc, là dạng hoàn toàn biệt hóa của Primordia Bloom.</t>
+          <t>Một Tacet Discord hình người sinh ra từ biển sâu, mang dáng dấp quý tộc, là dạng hoàn toàn biệt hóa của Primordia Bloom.</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9714,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Một Discord hình người sinh ra từ vực biển sâu, mang hình dáng giống một hiệp sĩ quý tộc, là dạng hoàn toàn biệt hóa của Primordia Bloom.</t>
+          <t>Một Tacet Discord hình người sinh ra từ biển sâu, mang dáng dấp hiệp sĩ quý tộc, là dạng hoàn toàn biệt hóa của Primordia Bloom.</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9779,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Một Discord hình người sinh ra từ vực biển sâu, mang hình dáng giống một thương nhân quý tộc, là dạng hoàn toàn biệt hóa của Primordia Bloom.</t>
+          <t>Một Tacet Discord hình người sinh ra từ vực thẳm biển cả, mang dáng vẻ của một thương gia quý tộc, một hình thái hoàn toàn biệt hóa của Primordia Bloom.</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9844,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Một Discord thường được nhìn thấy lơ lửng trên các công trình lớn, giả vờ tạo dáng uy nghiêm như thể các tòa nhà là phần mở rộng của cơ thể nó. Hình bóng của nó hòa lẫn với kiến trúc, sừng sững như một gã khổng lồ đáng sợ.</t>
+          <t>Một Tacet Discord thường lơ lửng trên các công trình lớn, giả vờ tạo dáng uy nghiêm như thể những tòa nhà là phần mở rộng của cơ thể nó. Dáng vẻ của nó hòa lẫn với kiến trúc, sừng sững như một gã khổng lồ đầy đe dọa.</t>
         </is>
       </c>
     </row>
@@ -9910,9 +9911,9 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Một Discord vô hình trú ngụ trong cơ thể của một món đồ chơi nhồi bông lớn và cũ kỹ. 
-Hắn nuôi sống bản thân bằng nỗi sợ hãi và tiếng thét mà hình dáng đáng sợ của mình khơi gợi—những tần số mà hắn cho là ngon lành nhất. Thế nhưng, thứ thường lọt vào tai hắn lại là: "Nhìn cái đồ chơi bẩn thỉu kia kìa. Thật đáng thương..."
-Liệu hắn có chưa đủ đáng sợ? Những tần số đầy thương hại như vậy có thực sự ăn được không?</t>
+          <t>Một Tacet Discord vô hình trú ngụ trong thân xác của một món đồ chơi nhồi bông cũ kỹ, tả tơi. 
+Hắn nuôi sống bản thân bằng nỗi sợ hãi và tiếng thét kinh hoàng mà hình dáng đáng sợ của hắn khơi gợi—những tần số mà hắn thấy ngon lành nhất. Ấy vậy mà, thứ lọt vào tai hắn thường xuyên lại là: *"Nhìn cái đồ chơi bẩn thỉu kia kìa. Thật tội nghiệp..."*
+Lẽ nào hắn không đủ đáng sợ? Hay những tần số đầy thương hại này thực sự có thể ăn được?</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9978,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Một Discord vô hình trú ngụ trong cơ thể của một món đồ chơi nhồi bông lớn và cũ kỹ.</t>
+          <t>Một Tacet Discord vô hình trú ngụ trong thân xác của một món đồ chơi nhồi bông cũ kỹ, sờn rách.</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10043,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Từng là sinh vật còn sót lại trong Nimbus Sanctum, Lorelei đã đạt được trí tuệ nhờ sức mạnh của Sentinel Imperator, được giao nhiệm vụ thanh lọc các tần số nhiễm độc trôi nổi trên mây.</t>
+          <t>Từng là một sinh vật còn sót lại trong Nimbus Sanctum, Lorelei đã có được trí tuệ nhờ sức mạnh của Sentinel Imperator, được giao trọng trách thanh tẩy những tần số nhiễm độc trôi nổi trên mây.</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10173,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Một Discord hình rồng lang thang trên đỉnh Penitent's End vì lý do chưa rõ, nuốt chửng mọi tần số một cách bừa bãi.</t>
+          <t>Một Tacet Discord hình rồng ẩn náu trên đỉnh Penitent's End vì lý do bí ẩn, nuốt chửng mọi tần số mà không phân biệt.</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10238,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10303,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10368,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10433,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10498,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10562,7 +10563,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10627,7 +10628,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10693,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere - nơi hội tụ tất cả các tần số phân rã, được gọi là "Beyond". Nó hiện thân dưới dạng một Phù Thủy Ba Mặt của Âm Phủ.</t>
+          <t>Một Tacet Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere - nơi hội tụ mọi tần số suy tàn, gọi là "Vùng Ngoài". Nó hiện thân dưới dạng một Phù Thủy Ba Mặt của Âm Phủ.</t>
         </is>
       </c>
     </row>
@@ -10757,7 +10758,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Sinh vật thế giới khác đang say ngủ trên Avinoleum, một lời tiên tri được ban xuống cõi phàm trần bởi Thần Tính.</t>
+          <t>Sinh vật đến từ thế giới khác đang yên giấc trên Avinoleum, một lời tiên tri mà Thần Tính ban xuống cho cõi phàm trần.</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10823,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10888,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10953,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Người bảo vệ của Septimont, cư ngụ bên trong đấu trường cổ xưa. Một sư tử cái của chiến trận, được tạo nên từ đá và tiếng gầm vang vọng.</t>
+          <t>Người bảo hộ của Septimont, ngự tại đấu trường cổ xưa. Một sư tử chiến trận, rèn từ đá và tiếng gầm vang vọng.</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11018,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ân sủng và lời tiên tri thiêng liêng đã giáng thế, và Kẻ Báo Điềm vô diện giờ đây đứng trước cánh cổng.</t>
+          <t>Ân sủng và lời tiên tri thiêng liêng của họ đã giáng thế, và Kẻ Báo Điềm Vô Diện giờ đây đứng trước cổng thành.</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11083,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11148,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11213,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11278,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11343,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11408,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11473,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11538,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11603,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11668,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11733,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Kẻ săn mồi đỉnh cao tại Sanguis Plateaus. Nó trỗi dậy cùng Dark Tide dâng cao, báo hiệu sự khởi đầu của cuộc săn.</t>
+          <t>Kẻ săn mồi đỉnh cao trên Cao nguyên Sanguis. Nó trỗi dậy cùng thủy triều Hắc Ám dâng cao, báo hiệu cuộc săn bắt bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -11797,7 +11798,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Một lớp vỏ hình người được tạo thành từ bùn đen. Nó hòa nhập vào đám con mồi, kiên nhẫn chờ đợi những kẻ săn mồi mà nó được tạo ra để nuốt chửng.</t>
+          <t>Một lớp vỏ hình người cấu thành từ bùn đen nhánh. Nó hòa mình vào đám con mồi, kiên nhẫn chờ đợi những kẻ săn mồi mà nó được tạo ra để nuốt chửng.</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11863,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Một sinh vật đang say ngủ dưới đại dương, tàn tích tro tàn của vinh quang đã tắt lửa lâu rồi.</t>
+          <t>Một sinh vật đang say ngủ dưới đáy đại dương, tàn tro của vinh quang đã tắt lụi từ lâu.</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11930,7 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>Thành viên của Midnight Rangers.
-Midnight Rangers bao gồm ba bộ phận: Outriders (trinh sát), Vanguard (tác chiến tấn công) và Rearguard (tác chiến phòng thủ), tất cả đều dưới sự chỉ huy của Đại tướng Jiyan.</t>
+Midnight Rangers gồm ba bộ phận: Outriders (trinh sát), Vanguard (tác chiến tấn công) và Rearguard (tác chiến phòng thủ), tất cả đều dưới sự chỉ huy của Đại Tướng Jiyan.</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11995,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Một thành viên của Midnight Rangers.</t>
+          <t>Thành viên của Midnight Rangers.</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12062,7 @@
       <c r="M178" t="inlineStr">
         <is>
           <t>Thành viên của Midnight Rangers.
-Midnight Rangers bao gồm ba bộ phận: Outriders (trinh sát), Vanguard (tác chiến tấn công) và Rearguard (tác chiến phòng thủ), tất cả đều dưới sự chỉ huy của Đại tướng Jiyan.</t>
+Midnight Rangers gồm ba bộ phận: Outriders (trinh sát), Vanguard (tác chiến tấn công) và Rearguard (tác chiến phòng thủ), tất cả đều dưới sự chỉ huy của Đại Tướng Jiyan.</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12127,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Một thành viên của Midnight Rangers.</t>
+          <t>Thành viên của Midnight Rangers.</t>
         </is>
       </c>
     </row>
@@ -12193,9 +12194,9 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Một thành viên băng đảng ngầm ở Ragunna.
-Trong một thời kỳ hỗn loạn của lịch sử Ragunna, nhiều người Ragunnesi bị đẩy vào các hoạt động băng đảng. Một số vì sinh tồn, số khác để tự vệ. Những chiếc mặt nạ từng tượng trưng cho lễ hội và ăn mừng giờ đây trở thành công cụ che giấu khuôn mặt khi họ thực hiện các hành vi bạo lực.
-Ngày nay, số ít thành viên còn sót lại vẫn bám víu vào truyền thống này, như thể nó có thể giúp một số người nhớ lại thời kỳ đã qua—cái gọi là "thời kỳ hoàng kim" khi họ đắm chìm trong sự vô pháp và tự do lang thang mà không sợ hậu quả.</t>
+          <t>Thành viên băng đảng ngầm ở Ragunna.
+Trong một thời kỳ hỗn loạn của lịch sử Ragunna, nhiều người Ragunnesi bị đẩy vào các hoạt động băng đảng. Có người vì mưu sinh, kẻ khác để tự vệ. Những chiếc mặt nạ từng tượng trưng cho lễ hội và ăn mừng giờ đây trở thành công cụ che giấu, giấu mặt họ khi thực hiện những hành vi bạo lực.
+Ngày nay, số thành viên còn sót lại vẫn níu kéo truyền thống ấy, như thể muốn nhắc nhở ai đó về thời đã qua—cái gọi là "thời hoàng kim", khi họ đắm chìm trong sự vô pháp, tự do lang thang mà chẳng sợ hậu quả.</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12261,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Một thành viên của băng đảng ngầm Ragunna.</t>
+          <t>Thành viên băng đảng ngầm ở Ragunna.</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12326,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12391,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12455,7 +12456,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Một Discord hình người cúi gập, với dòng điện chạy khắp các mạch máu và một phần phụ giống roi điện trên đầu.</t>
+          <t>Một Tacet Discord hình người gù lưng, với dòng điện chạy khắp cơ thể và một phần phụ giống roi trên đầu.</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12521,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12586,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ. Nó thu thập những tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12651,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12716,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Sau khi quét dữ liệu của các loài động vật trước đây tại Lahai-Roi, Exostrider đã sử dụng các bộ phận của chính mình để phát triển và nhân bản những con ong cơ khí. Do kích thước nhỏ và cấu tạo cơ thể độc đáo của drone, người Roya thường sử dụng chúng như công cụ để thu thập phấn hoa và mật hoa thực vật.</t>
+          <t>Sau khi quét dữ liệu về các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã sử dụng chính bộ phận của mình để tạo ra và nhân bản những con ong cơ khí. Do kích thước nhỏ và cấu tạo cơ thể đặc biệt, người dân Roya thường dùng chúng như công cụ để thu thập phấn hoa và mật hoa thực vật.</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12781,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Một chú ong nghệ cơ khí, được tạo ra từ chính các bộ phận của Exostrider. Người Roya thường sử dụng chúng như công cụ để thu thập phấn hoa và mật hoa thực vật.</t>
+          <t>Một chú ong nghệ thuật, được tạo ra từ chính các bộ phận của Exostrider. Người Roya thường dùng chúng để thu thập phấn hoa và mật hoa thực vật.</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12846,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Sau khi quét dữ liệu của các loài động vật trước đây ở Lahai-Roi, Exostrider đã sử dụng các bộ phận của chính mình để phát triển và nhân rộng những con ong mật cơ khí. Do kích thước nhỏ và cấu tạo cơ thể độc đáo, Roya thường sử dụng chúng như công cụ để thu thập các khoáng vật dễ vỡ từ những không gian chật hẹp.</t>
+          <t>Sau khi quét dữ liệu về các loài động vật trước đây ở Lahai-Roi, Exostrider đã sử dụng chính các bộ phận của mình để phát triển và nhân bản những con ong máy. Nhờ kích thước nhỏ và cấu tạo đặc biệt, người Roya thường dùng chúng để thu thập các loại khoáng vật mỏng manh từ những không gian chật hẹp.</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12911,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Một con ong nghệ cơ khí, được tạo ra từ các bộ phận của Exostrider. Người Roya thường sử dụng chúng như công cụ để thu thập các loại khoáng vật dễ vỡ từ những không gian chật hẹp.</t>
+          <t>Một chú ong nghệ thuật, được tạo ra từ chính các bộ phận của Exostrider. Người Roya thường dùng chúng để thu thập các loại khoáng vật dễ vỡ từ những không gian chật hẹp.</t>
         </is>
       </c>
     </row>
@@ -12975,7 +12976,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Một robot thám hiểm do Tập đoàn Spacetrek phát triển. Linh hoạt và nhanh nhẹn, nó hoàn toàn phù hợp với địa hình gồ ghề của Lahai-Roi.</t>
+          <t>Một rô-bốt thám hiểm do Spacetrek Collective phát triển. Nhanh nhẹn và linh hoạt, hoàn toàn phù hợp với địa hình gồ ghề của Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13041,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Những Roya bị bộ tộc trục xuất vì bán xác tế bào Exostrider. Tuy nhiên, họ tự coi mình không bị ràng buộc bởi những lề thói cũ. Để chế giễu truyền thống, họ đeo mặt nạ làm từ đầu Exoswarm và sử dụng Shepherd's Staff làm vũ khí, từ đó trở thành thế lực hỗn loạn không kiểm soát tại Lahai-Roi.</t>
+          <t>Những người Roya bị trục xuất khỏi bộ tộc vì bán tế bào Exostrider. Nhưng với họ, điều đó có nghĩa là được giải phóng khỏi những lề thói cũ. Để chế giễu truyền thống, họ đeo mặt nạ làm từ đầu Bầy Ngoại Ký và sử dụng Gậy Người Chăn Cừu như vũ khí, trở thành thế lực hỗn loạn không gì kiềm chế nổi ở Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -13105,7 +13106,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Những Roya man rợ và tàn bạo đã phá vỡ truyền thống và bị trục xuất khỏi bộ tộc.</t>
+          <t>Những kẻ Roya hoang dã và tàn bạo, phản bội truyền thống và bị bộ tộc ruồng bỏ.</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13171,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Những Roya man rợ và tàn bạo đã phá vỡ truyền thống và bị trục xuất khỏi bộ tộc.</t>
+          <t>Những kẻ Roya hoang dã và tàn bạo, phản bội truyền thống và bị bộ tộc ruồng bỏ.</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13236,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Một loại Tacet Discord Murmurin bọc thép điện từ có khả năng hút kim loại để tạo thành lớp vỏ bảo vệ xung quanh. Những tia lửa điện mờ nhạt có thể nhìn thấy qua các vết nứt trên lớp giáp kim loại của nó.</t>
+          <t>Một loại Murmurin TD điện từ bọc thép, thu hút kim loại để tạo thành lớp vỏ bảo vệ quanh mình. Những tia điện lóe lên mờ ảo qua các vết nứt trên bộ giáp kim loại.</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13301,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -13365,7 +13366,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13431,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Một loại mech do Spacetrek Collective phát triển, có các biến thể cận chiến và tầm xa. Hai mẫu này chiến đấu nhịp nhàng khi được ghép cặp.</t>
+          <t>Một loại mech do Spacetrek Collective phát triển, có biến thể cận chiến và tầm xa. Hai mẫu này chiến đấu ăn ý và duyên dáng khi kết hợp cùng nhau.</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13496,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Một loại mech do Spacetrek Collective phát triển, có các biến thể cận chiến và tầm xa. Hai mẫu này chiến đấu nhịp nhàng khi được ghép cặp.</t>
+          <t>Một loại mech do Spacetrek Collective phát triển, có biến thể cận chiến và tầm xa. Hai mẫu này chiến đấu ăn ý và duyên dáng khi kết hợp cùng nhau.</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13561,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Một con tuần lộc cơ khí, được tạo ra từ chính các bộ phận của Exostrider. Chúng thường giúp đỡ Roya trong việc tìm kiếm thực vật.</t>
+          <t>Một con tuần lộc cơ khí, được tạo ra từ chính các bộ phận của Exostrider. Chúng thường giúp người Roya tìm kiếm thực vật.</t>
         </is>
       </c>
     </row>
@@ -13625,7 +13626,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Một chú tuần lộc cơ khí, được tạo ra từ chính các bộ phận của Exostrider. Chúng thường hỗ trợ Roya trong việc khai thác quặng.</t>
+          <t>Một con tuần lộc cơ khí, được tạo ra từ chính các bộ phận của Exostrider. Chúng thường hỗ trợ người Roya trong việc khai thác quặng.</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13691,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Một con bò xạ cơ khí, được tạo ra từ chính các bộ phận của Exostrider. Chúng thường giúp đỡ Roya trong việc vận chuyển hàng hóa.</t>
+          <t>Một con bò xạ cơ khí, được tạo ra từ chính các bộ phận của Exostrider. Chúng thường giúp người Roya vận chuyển hàng hóa.</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13756,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Một cỗ máy cơ khí lớn di chuyển nhanh, được phát triển bởi Spacetrek Collective cho cả mục đích vận tải và phòng thủ.</t>
+          <t>Một cỗ máy cơ khí lớn, di chuyển nhanh, do Spacetrek Collective phát triển để vận chuyển và phòng thủ.</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13821,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Một cỗ máy săn mồi hung hãn lang thang trong vùng hoang dã Lahai-Roi, săn đuổi bất kỳ dấu hiệu chuyển động nào.</t>
+          <t>Một cỗ máy săn mồi hung hãn lang thang trong hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào.</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13886,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Một sinh vật ký sinh sống bên trong Whisperin Tacet Discord. Nó sử dụng cơ thể vật chủ như một cái kén và hấp thụ tần số của vật chủ.</t>
+          <t>Một sinh vật ký sinh sống bên trong Tacet Discord Whisperin. Nó dùng cơ thể vật chủ như kén và hấp thụ tần số của chúng.</t>
         </is>
       </c>
     </row>
@@ -13950,7 +13951,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Một sinh vật ký sinh sống bên trong Whisperin Tacet Discord. Nó sử dụng cơ thể vật chủ như một cái kén và hấp thụ tần số của vật chủ.</t>
+          <t>Một sinh vật ký sinh sống bên trong Tacet Discord Whisperin. Nó dùng cơ thể vật chủ như kén và hấp thụ tần số của chúng.</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14016,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Một trong những Overseer của Fractsidus. Ngọn lửa rực cháy của hắn thiêu rụi mọi trật tự và quy tắc, để lại hỗn loạn sau đó.</t>
+          <t>Một trong những Fractsidus Overseer. Ngọn lửa rực cháy của hắn thiêu rụi mọi trật tự và quy tắc, để lại hỗn loạn trong tro tàn.</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14081,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere - nơi hội tụ tất cả các tần số phân rã, được gọi là "Beyond". Nó hiện thân dưới dạng một Phù Thủy Ba Mặt của Âm Phủ.</t>
+          <t>Một Tacet Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere - nơi hội tụ mọi tần số suy tàn, gọi là "Vùng Ngoài". Nó hiện thân dưới dạng một Phù Thủy Ba Mặt của Âm Phủ.</t>
         </is>
       </c>
     </row>
@@ -14146,8 +14147,8 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Đám đông đồng thanh xướng tên Ngài; vô số giọng ca tôn vinh phúc âm của ngày tận thế.
-Ngài và vương quốc của Ngài đã định sẵn sẽ giáng thế.</t>
+          <t>Đám đông đồng thanh hô vang danh Người; vô số giọng nói ca tụng lời tiên tri về ngày tận thế.
+Người và vương quốc của Người đã định sẵn phải sụp đổ.</t>
         </is>
       </c>
     </row>
@@ -14212,7 +14213,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Mảng dò đầu tiên của Spacetrek Collective được xây dựng tại Sundermere để giám sát và ổn định trạng thái năng lượng của Reactor Drive trong thời gian thực.</t>
+          <t>Mảng dò tìm đầu tiên của Hội Tập Đoàn Spacetrek được xây dựng tại Sundermere để giám sát và ổn định trạng thái năng lượng của Lò Phản Ứng Drive theo thời gian thực.</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14278,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Một bộ phận của Reactor Drive. Khi phản ứng miễn dịch của Drive được kích hoạt, logic chiến đấu của nó sẽ khởi động để loại bỏ mọi kẻ xâm nhập.</t>
+          <t>Linh kiện của Bộ Phản Ứng. Khi phản ứng miễn dịch của Bộ Phản Ứng kích hoạt, logic chiến đấu của nó sẽ khởi động để loại bỏ mọi kẻ xâm nhập.</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14343,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Một sinh vật đến từ chiều không gian cao hơn, bắt nguồn từ Aleph-1, đã định hình cơ thể mình từ Exoswarm bị Void Storm nuốt chửng và rèn cột sống từ tàn tích của Exostrider. Đối với cư dân Lahai-Roi, Voidworm và Void Storm đều đáng sợ như nhau. Cả hai đều là những thảm họa tự nhiên khó lường, nuốt chửng mọi thứ trên đường đi.</t>
+          <t>Một sinh vật siêu chiều đến từ Aleph-1, hình thành cơ thể từ Exoswarm bị Void Storm nuốt chửng và tạo dựng xương sống từ tàn tích của Exostrider. Đối với cư dân Lahai-Roi, Voidworm và Void Storm đều đáng sợ như nhau. Cả hai đều là thảm họa tự nhiên khó lường, nuốt chửng mọi thứ trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14410,9 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Bóng tối ẩn hiện trong cát bụi và bão tố.</t>
+          <t>Một bóng đen ẩn hiện trong cát và bão.
+Một thứ quái dị dệt từ hàng vạn Exoswarm.
+Hãy lắng nghe — ngôi sao hư vô đang ngân nga, và nó đã gần rồi.</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14477,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Một TD hình người duyên dáng khoác lên mình lớp băng giá.</t>
+          <t>Một Tacet Discord hình người duyên dáng, khoác lên mình lớp băng giá.</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14542,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Một Discord hình người không mặt, cơ thể có thể chảy, tách rời và hợp nhất như một bóng tối sống động.</t>
+          <t>Một Tacet Discord hình người không mặt, thân thể trôi chảy, tách rời và hợp nhất như một bóng tối sống động.</t>
         </is>
       </c>
     </row>
@@ -14604,7 +14607,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Một Exoswarm hình dáng chim săn mồi bí ẩn, dường như bắt chước một loài động vật cổ đại đã tuyệt chủng.</t>
+          <t>Một Exoswarm hình dáng chim săn mồi bí ẩn, dường như bắt chước loài động vật cổ đại đã tuyệt chủng.</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14672,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Một loài chim săn mồi hùng mạnh được cho là đã tuyệt chủng, giờ đây xuất hiện trong Upphaf Life Chamber.</t>
+          <t>Một loài mãnh thú săn mồi hùng mạnh từng bị cho là tuyệt chủng, nay lại xuất hiện trong Upphaf Life Chamber.</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14737,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Trong số Exoswarm, không ai cao lớn hơn hay nhận được sự tôn kính nhiều hơn những cá thể khổng lồ này. Chúng được coi là những người dẫn đường đáng tin cậy, dẫn dắt đồng loại trở về với Exostrider.</t>
+          <t>Trong đám Exoswarm, không có kẻ nào cao lớn hơn hay được tôn kính hơn những gã khổng lồ này. Chúng được coi là những người dẫn đường đáng tin cậy, dẫn dắt đồng loại trở về với Exostrider.</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14802,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Một cỗ máy đen không lời, lạc lõng và khao khát trở về nhà.</t>
+          <t>Một cỗ máy đen im lặng, lạc lõng và khao khát trở về nhà.</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14867,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Di tích cổ đại bị chôn vùi dưới lớp băng vĩnh cửu, tự giam cầm chính mình.</t>
+          <t>Một tàn tích cổ đại bị chôn vùi dưới lớp băng vĩnh cửu, tự giam cầm chính mình.</t>
         </is>
       </c>
     </row>
@@ -14931,9 +14934,9 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Một tác phẩm quý giá của Fractsidus.
-Sử dụng công nghệ của New Federation, chúng đã kết hợp một bộ móng vuốt hung ác với bản chất của Discord, tạo ra một vũ khí tàn nhẫn có thể siết cổ con mồi trước khi xé xác.
-Tuy nhiên, mọi sự siêu việt đều phải trả giá. Những kẻ đón nhận sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái vỏ rỗng tuếch.</t>
+          <t>Kiệt tác của Fractsidus.
+Bằng công nghệ của Liên Bang Mới, họ đã kết hợp bộ móng vuốt sắc nhọn với tinh hoa của Tacet Discord, tạo ra một vũ khí tàn nhẫn có thể bóp cổ con mồi trước khi xé xác chúng.
+Nhưng mọi sự vượt trội đều phải trả giá. Những kẻ sử dụng sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái xác rỗng tuếch.</t>
         </is>
       </c>
     </row>
@@ -14998,7 +15001,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Một tác phẩm quý giá của Fractsidus, kết hợp bộ móng vuốt hung dữ với tinh hoa của Discord bằng công nghệ của New Federation.</t>
+          <t>Kiệt tác của Fractsidus, kết hợp bộ móng vuốt sắc nhọn với tinh hoa của Tacet Discord cùng công nghệ của Liên Bang Mới.</t>
         </is>
       </c>
     </row>
@@ -15065,9 +15068,9 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Một sáng tạo quý giá của Fractsidus.
-Sử dụng công nghệ của New Federation, họ đã kết hợp đôi tay áo bay phấp phới với tinh hoa của một Discord, tạo ra những chiếc miệng há rộng có khả năng nuốt chửng chính tần số của con mồi.
-Tuy nhiên, mọi sự siêu việt đều phải trả giá. Những kẻ đón nhận sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái vỏ rỗng tuếch.</t>
+          <t>Kiệt tác của Fractsidus.
+Bằng công nghệ của Liên Bang Mới, họ đã kết hợp đôi tay áo bay lượn với tinh hoa của Tacet Discord, tạo ra những chiếc miệng há rộng có thể nuốt chửng cả tần số của con mồi.
+Nhưng mọi sự vượt trội đều phải trả giá. Những kẻ sử dụng sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái xác rỗng tuếch.</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15135,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Một tác phẩm quý giá của Fractsidus, kết hợp đôi tay áo bay với bản chất của một Discord bằng công nghệ của New Federation.</t>
+          <t>Kiệt tác của Fractsidus, kết hợp đôi tay áo bay lượn với tinh hoa của Tacet Discord cùng công nghệ của Liên Bang Mới.</t>
         </is>
       </c>
     </row>
@@ -15197,7 +15200,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Tác phẩm quý giá của Fractsidus, kết hợp chiếc mũ hình tranh với tinh hoa của một Discord bằng công nghệ của New Federation.</t>
+          <t>Kiệt tác của Fractsidus, kết hợp chiếc mũ rộng vành với tinh hoa của Tacet Discord cùng công nghệ của Liên Bang Mới.</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15265,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Một sản phẩm của Fractsidus. Một thất bại lỗi bị bỏ rơi trong bóng tối.</t>
+          <t>Một sản phẩm của Fractsidus. Một thất bại dị dạng bị vứt bỏ vào bóng tối.</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15330,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Một sản phẩm của Fractsidus. Một thất bại lỗi bị bỏ rơi trong bóng tối.</t>
+          <t>Một sản phẩm của Fractsidus. Một thất bại dị dạng bị vứt bỏ vào bóng tối.</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15395,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Một sản phẩm của Fractsidus. Một thất bại lỗi bị bỏ rơi trong bóng tối.</t>
+          <t>Một sản phẩm của Fractsidus. Một thất bại dị dạng bị vứt bỏ vào bóng tối.</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15460,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>TD giống bướm đêm độc đáo đặc hữu của Dimmr Plains, thường xuất hiện ở những khu vực bị Voidmatter ô nhiễm nặng.</t>
+          <t>Một loài **Tacet Discord** giống bướm đêm đặc hữu ở **Dimmr Plains**, thường xuất hiện ở những khu vực bị **Voidmatter** ô nhiễm nặng.</t>
         </is>
       </c>
     </row>
@@ -15525,10 +15528,10 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Một kẻ canh giữ đến từ bên kia Stridergate, được tạo ra theo thiết kế của Aleph-1.
-Trước những ai tìm kiếm câu trả lời, Aleph-1 phô bày chính ranh giới của tri thức: thứ từng mở ra con đường đến tương lai giờ đây đã trở thành điều gì đó tối tăm và đáng sợ ngoài sức tưởng tượng.
+          <t>Một kẻ canh giữ đến từ bên kia Cổng Strider, sinh ra từ thiết kế của Aleph-1.
+Trước những ai tìm kiếm câu trả lời, Aleph-1 chiếu lên ranh giới của tri thức: thứ từng mở ra con đường đến tương lai giờ đã biến thành điều gì đó tối tăm và đáng sợ không thể nhận ra.
 Ở quy mô vũ trụ, sự sống và hy vọng chỉ là những điều tầm thường, không có ý nghĩa.
-Mọi thứ chỉ là sự khởi đầu không có kết thúc. Mọi thứ chỉ là sự theo đuổi vô nghĩa.</t>
+Mọi thứ chỉ là khởi đầu không có kết thúc. Mọi thứ chỉ là sự theo đuổi vô nghĩa.</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15596,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Trên quy mô vũ trụ, sự sống và hy vọng chỉ là những điều tầm thường, không có ý nghĩa.</t>
+          <t>Trên quy mô vũ trụ, sinh mệnh và hy vọng chỉ là những điều tầm thường, không có ý nghĩa gì.</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15661,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>"Sinh viên khoa Voidmatters tại Startorch Academy. Luôn sẵn sàng nở nụ cười 'dịu dàng' với mọi người."</t>
+          <t>"Sinh viên Khoa Vật Chất Hư Không tại Học viện Startorch. Luôn sẵn sàng nở nụ cười 'dịu dàng' với tất cả mọi người."</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15726,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Một Whisperin TD cấp Common phân bố rộng rãi trong tự nhiên. Cơ thể nhỏ bé của nó mỏng manh như băng.</t>
+          <t>Một Tacet Discord cấp thường phân bố rộng rãi ngoài tự nhiên. Thân hình nhỏ bé của nó mỏng manh như băng giá.</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15791,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Takes place in {0}</t>
+          <t>Diễn ra tại {0}</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15921,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Test Center - {0}</t>
+          <t>Trung tâm kiểm tra - {0}</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15986,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Đánh bại Chief Assessor ≥ {0} lần</t>
+          <t>Đánh bại Người Giám Định Trưởng ≥ {0} lần</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16051,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Suggested Lv. {0}</t>
+          <t>Cấp đề xuất: {0}</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16116,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Current Wave: {0}</t>
+          <t>Làn Sóng Hiện Tại: {0}</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16181,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Đã hoàn thành tất cả mục tiêu test. Bạn có thể chọn rời đi hoặc tiếp tục chiến đấu.</t>
+          <t>Đã hoàn thành tất cả mục tiêu thử nghiệm. Ngươi có thể chọn rời đi hoặc tiếp tục chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16376,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Chief Assessor Bị Đánh Bại: &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0}</t>
+          <t>Đánh bại Người Giám Định Trưởng: &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0}</t>
         </is>
       </c>
     </row>
@@ -16504,8 +16507,8 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>"Quit Test" sẽ kết thúc lần thử này và đưa bạn trở lại trang Test Details.
-"Làm Lại Kiểm Tra" sẽ khởi động lại "Kiểm Tra Sơ Bộ" với cùng đội hình.</t>
+          <t>"Bỏ bài kiểm tra" sẽ kết thúc lượt thử này và đưa bạn về trang Chi tiết bài kiểm tra.
+"Làm lại bài kiểm tra" sẽ khởi động lại "Bài kiểm tra sơ bộ" với cùng đội hình.</t>
         </is>
       </c>
     </row>
@@ -16571,8 +16574,8 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>"Quit Test" sẽ kết thúc lần thử này và đưa bạn trở lại trang Test Details.
-"Làm Lại Kiểm Tra" sẽ khởi động lại "Kiểm Tra Cuối Cùng" với cùng đội hình.</t>
+          <t>"Bỏ bài kiểm tra" sẽ kết thúc lượt thử này và đưa bạn về trang Chi tiết bài kiểm tra.
+"Làm lại bài kiểm tra" sẽ khởi động lại "Bài kiểm tra cuối cùng" với cùng đội hình.</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16705,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành mục tiêu. Không thể nhận thưởng</t>
+          <t>Chưa hoàn thành nhiệm vụ. Không thể nhận thưởng</t>
         </is>
       </c>
     </row>
@@ -16767,7 +16770,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng. Không thể nhận lại</t>
+          <t>Đã nhận phần thưởng rồi. Không thể nhận lại</t>
         </is>
       </c>
     </row>
@@ -16832,7 +16835,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mở khóa. Không thể vào trung tâm test</t>
+          <t>Chưa đáp ứng đủ yêu cầu mở khóa. Không thể vào trung tâm thử nghiệm</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16900,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành Test Sơ bộ. Không thể tiến vào Test Cuối cùng.</t>
+          <t>Chưa hoàn thành Bài Kiểm Tra Sơ Bộ. Không thể tham gia Bài Kiểm Tra Chung Kết</t>
         </is>
       </c>
     </row>
@@ -16962,7 +16965,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu.</t>
+          <t>Sự kiện chưa bắt đầu đâu.</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17030,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Giai đoạn này sẽ mở khóa trong {0}.</t>
+          <t>Giai đoạn này sẽ mở khóa vào {0}.</t>
         </is>
       </c>
     </row>
@@ -17157,7 +17160,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Chỉ số bị khóa. Không thể chỉnh sửa.</t>
+          <t>Thuộc tính bị khóa. Không thể thay đổi.</t>
         </is>
       </c>
     </row>
@@ -17287,7 +17290,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Suggested Lv. {0}</t>
+          <t>Cấp đề xuất: {0}</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17355,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Current Points: {0}</t>
+          <t>Điểm hiện tại: {0}</t>
         </is>
       </c>
     </row>
@@ -17482,7 +17485,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Total Points đạt {0}</t>
+          <t>Tổng Điểm đạt {0}</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17550,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Giai đoạn Tactical Simulacra mới đã mở khóa.</t>
+          <t>Giai đoạn Chiến Thuật Mô Phỏng mới đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17615,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Buffs đã chọn: {0}/{1}</t>
+          <t>Hiệu ứng đã chọn: {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -17677,7 +17680,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Highest Record: {0}</t>
+          <t>Kỷ Lục Cao Nhất: {0}</t>
         </is>
       </c>
     </row>
@@ -17742,7 +17745,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Synchro Coins: {0}/{1}</t>
+          <t>Đồng Tiền Đồng Bộ: {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17810,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Đội hình của bạn vẫn chưa hoàn chỉnh. Bạn có chắc chắn muốn bắt đầu thử thách?</t>
+          <t>Đội hình của cậu vẫn chưa đủ. Cậu chắc chắn muốn bắt đầu thử thách chứ?</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17875,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đạt {0} điểm trong giai đoạn hiện tại</t>
+          <t>Đạt {0} điểm ở giai đoạn hiện tại</t>
         </is>
       </c>
     </row>
